--- a/naver-place-crawler/results_nail/성동_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/성동_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V102"/>
+  <dimension ref="A1:V182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9879,30 +9879,34 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>프랜차이즈본사</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>정원뷰티</t>
+          <t>마틴네일스튜디오</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>shawns98@naver.com</t>
+          <t>samccochu@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1392-1528</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>서울특별시 성동구 아차산로 68 에이유빌딩 8층</t>
+          <t>서울특별시 성동구 왕십리로4길 24-21 2층</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.allbeauty22.com/</t>
+          <t>https://www.instagram.com/mtn.nailstudio</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9937,30 +9941,7490 @@
         </is>
       </c>
       <c r="P102" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>19</v>
+      </c>
+      <c r="R102" t="n">
+        <v>129</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>1261222898</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1261222898</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>씨티네일 성수점</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>kkl430@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 아차산로 104 지하1층</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>2421</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>39</v>
+      </c>
+      <c r="R103" t="n">
+        <v>2460</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>1261267776</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1261267776</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>쩡네일</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>jjunge2944@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0507-1351-4996</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 용답중앙길 58 1층</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>http://instagram.com/andaepyo010</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>211</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>125</v>
+      </c>
+      <c r="R104" t="n">
+        <v>336</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>1978483187</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1978483187</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>위드앤샵 네일</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>kayladaily@naver.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 317 2층</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sOUGkKHd</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>45</v>
+      </c>
+      <c r="R105" t="n">
+        <v>87</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>20877184</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20877184</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>루나네일</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>lunamika@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>02-2282-1260</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로 22 1층 루나네일</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lunamika</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>3</v>
+      </c>
+      <c r="R106" t="n">
+        <v>49</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>36178184</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36178184</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>더제이네일</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>creamsand@naver.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0507-1330-4591</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 용답29길 28-1 1층 더 제이 네일</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>http://instagram.com/the_jnail</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q107" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="R107" t="n">
+        <v>36</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>1110945597</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110945597</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>공간네일 금호점</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>tauen2000@naver.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0507-1361-7732</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 158-2 3층 301호</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gonggan_gh</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>1040</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>36</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1076</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>1541708607</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1541708607</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>마리네일</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>hydestocker@naver.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>070-8225-7211</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마조로 24</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>15</v>
+      </c>
+      <c r="R109" t="n">
+        <v>26</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>37638325</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37638325</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>로맨틱네일</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>dahxxxn@naver.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0507-1429-5055</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 117 금호자이1차아파트 상가 지하2층 17호</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>http://instagram.com/theromantic_nail</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>12</v>
+      </c>
+      <c r="R110" t="n">
+        <v>23</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>1843436062</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1843436062</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>네일상상</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>mimi_talk@naver.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0507-1314-4133</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로 84 한진종합상가 1층 116-1호</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mimi_talk</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>23</v>
+      </c>
+      <c r="R111" t="n">
+        <v>131</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>1073035676</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1073035676</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>더네일갤러리</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ym851218@naver.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>02-499-5620</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 89 성동구민체육센터 내 1층</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1</v>
+      </c>
+      <c r="R112" t="n">
+        <v>1</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>37243945</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37243945</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>이오네일 성수</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2onail_@naver.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0507-1494-2894</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 연무장7길 12 4층 402호</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/2onail_</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>586</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>110</v>
+      </c>
+      <c r="R113" t="n">
+        <v>696</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>1606121008</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1606121008</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>네일뮤지크</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>do0ogi@naver.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0507-1384-1155</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 매봉길 48 힐스타운 5층</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>11</v>
+      </c>
+      <c r="R114" t="n">
+        <v>29</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>1865910213</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1865910213</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>팅커벨네일아트</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>dailydessert@naver.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0507-1306-2355</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마조로 17 1층 12호</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>http://instagram.com/tinkerbellnail</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>80</v>
+      </c>
+      <c r="R115" t="n">
+        <v>671</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>20332216</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20332216</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>코지네일샵</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>syjang128@naver.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>02-2200-1543</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당동 168-1 비트플렉스 3층 기-03-81호</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>101</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>19989967</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19989967</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>네일 유노이아</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>janhaeji@naver.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0507-1473-8779</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 378</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>3</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>1510553416</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1510553416</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>푸스케어 성수뚝섬점</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jyhjyh1058@naver.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0507-1322-6859</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로10길 6 서울숲비즈포레 1층 102호</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fusscare_ttukseom/</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>156</v>
+      </c>
+      <c r="R118" t="n">
+        <v>384</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>1482300091</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1482300091</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>봉숭아 손톱</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>mom6005@naver.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>02-2297-4135</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로 87 3층</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>2</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>935379402</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/935379402</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>린지네일</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>linzy3625@naver.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로6길 2</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>http://linzynail23.blog.me/</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>429</v>
+      </c>
+      <c r="R120" t="n">
+        <v>455</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>33851083</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33851083</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>오어즈네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>oarsnailstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0507-1412-9505</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원1길 39 4층</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_UxbxlAn</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>6</v>
+      </c>
+      <c r="R121" t="n">
+        <v>62</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>1176796230</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1176796230</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>풋풋한리쌤 성수본점</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>cute6063@naver.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0507-1357-0675</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 아차산로 91 6층</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCXN_i4oAs4X7L9I5_5i1L7Q</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>18</v>
+      </c>
+      <c r="R122" t="n">
+        <v>256</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>1995967265</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1995967265</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>네일힐</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>rrttdd0724@naver.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호산길 28 1층</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_nailhill_</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1</v>
+      </c>
+      <c r="R123" t="n">
+        <v>33</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>1959213642</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1959213642</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>쿠킹네일</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>angel_0911@naver.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>0507-1419-3600</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로6길 50 101동 125호 쿠킹네일</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cooking_nail</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>829</v>
+      </c>
+      <c r="Q124" t="n">
         <v>31</v>
       </c>
-      <c r="R102" t="n">
+      <c r="R124" t="n">
+        <v>860</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>1040198201</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040198201</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>피노네일</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>hankyuldata@naver.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>0507-1360-3051</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 뚝섬로 393 1층 피노네일</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ppino_nail/</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>311</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>16</v>
+      </c>
+      <c r="R125" t="n">
+        <v>327</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>1142566704</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1142566704</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>한나의 네일</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>pvc1120@naver.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 217-1 2층</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hannah.s_nail/</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>13</v>
+      </c>
+      <c r="R126" t="n">
+        <v>73</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>1669116810</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1669116810</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>jin 네일</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>jin_nail6453@naver.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>02-2291-4400</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 하왕십리동 700</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jinnail4400/</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>5</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>569558064</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/569558064</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>벨라 앤</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jhham11@naver.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>02-2282-1788</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 고산자로 132 102호</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>12</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>1877017944</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1877017944</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>조이네일</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>nailheimish@naver.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0507-1330-4862</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로17길 5</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/joynail__?igsh=MTMzdzRwY3ZmdDVr</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>15</v>
+      </c>
+      <c r="R129" t="n">
+        <v>164</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>498538913</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/498538913</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>누아네일</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>cjfng@naver.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0507-1479-2918</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로4길 26-20 2층</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nuanail_</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>227</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>193</v>
+      </c>
+      <c r="R130" t="n">
+        <v>420</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>1942249674</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1942249674</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>네일,엘린</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jiayou1121@naver.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0507-1325-6175</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마장로 137 221동 1층 1169호 (상왕십리동, 텐즈힐)</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/elin__0208</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>8</v>
+      </c>
+      <c r="R131" t="n">
+        <v>12</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>1043605992</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1043605992</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>픽시네일</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>althcjstk603@naver.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0507-1412-9558</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 177 1층</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_PmxoxjG</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>36</v>
+      </c>
+      <c r="R132" t="n">
+        <v>96</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>255406085</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/255406085</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>네일스타일 왕십리점</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>alsltogo@naver.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리광장로 17 왕십리역 엔터식스 B1 네일스타일</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailstyle.kr/</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>6</v>
+      </c>
+      <c r="R133" t="n">
+        <v>204</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>1202128561</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1202128561</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>무온</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>hiksoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0507-1362-1945</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 고산자로 275 102호</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muon__nail/</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>10</v>
+      </c>
+      <c r="R134" t="n">
+        <v>49</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>2034901208</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2034901208</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>네일원</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>nail_one@naver.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0507-1356-8112</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 고산자로 232 1층</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_VxlxiMxb</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>7</v>
+      </c>
+      <c r="R135" t="n">
+        <v>115</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>1668122389</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1668122389</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>누네일 왕십리점</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>wldud8222@naver.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0507-1378-4798</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학봉28길 4 1층</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wldud8222</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>715</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>65</v>
+      </c>
+      <c r="R136" t="n">
+        <v>780</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>1040994887</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040994887</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>루시네일</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>hyeoniizzang@naver.com</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원길 50 3층 302호</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>http://instagram.com/lucynail486</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>8</v>
+      </c>
+      <c r="R137" t="n">
+        <v>19</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>1491143356</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1491143356</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>몽그리네일</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>cherry__0418@naver.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로21길 12 2층</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_cwPUb</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>3842</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>21</v>
+      </c>
+      <c r="R138" t="n">
+        <v>3863</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>1645651713</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1645651713</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>네일 르씨엘</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>yun5164@naver.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0507-1315-4179</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 332 성동트레비스타 304호</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_le_ciel</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>26</v>
+      </c>
+      <c r="R139" t="n">
+        <v>66</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>1173919796</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1173919796</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>보리네일</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>kd_43@naver.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>0507-1326-4541</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 86 1층</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>http://instagram.com/bori_nail</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>5</v>
+      </c>
+      <c r="R140" t="n">
         <v>31</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>1398373917</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1398373917</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>네일살롱바이선하</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>sy170416@naver.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 40 힐스테이트 서울숲리버 상가 1층</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>67</v>
+      </c>
+      <c r="R141" t="n">
+        <v>72</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>1085149223</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1085149223</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>오호네일 성수</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>hohomiu2@naver.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0507-1356-1440</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 둘레9나길 7 1층</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ohho_nail</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>23</v>
+      </c>
+      <c r="R142" t="n">
+        <v>241</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>1299662515</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1299662515</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>다교네일 성수</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>dakyonailcute-2@naver.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0507-1448-0707</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 연무장15길 11 가B동 3층 305호</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_QDzxfG/chat</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>545</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>38</v>
+      </c>
+      <c r="R143" t="n">
+        <v>583</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>1936716654</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1936716654</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>느보네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로31길 8 1층 102호 느보네일스튜디오</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_sHxdvxj</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>11</v>
+      </c>
+      <c r="R144" t="n">
+        <v>31</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>1443702098</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1443702098</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>제이벨네일</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>everydaylovemoment@naver.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0507-1334-1131</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수일로4길 25 103호</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/j.belle_shan/</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>6</v>
+      </c>
+      <c r="R145" t="n">
+        <v>252</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>1261524364</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1261524364</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>릴리하우스</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>thelilyhouse@naver.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0507-1409-0938</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 뚝섬로 391-3 1층</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_lilyhouse/profilecard</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>30</v>
+      </c>
+      <c r="R146" t="n">
+        <v>245</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>1664972350</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1664972350</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>네일바이현</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>leeborabora@naver.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0507-1366-6784</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 410 E동 2층 202호</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_by_hyun3554</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>40</v>
+      </c>
+      <c r="R147" t="n">
+        <v>278</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>1509747487</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1509747487</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>큐릭스 왕십리점</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>qmdlthsuwkd@naver.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0507-1360-3400</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로6길 50 101동 1층 121호</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cureix_wangsimni</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>21</v>
+      </c>
+      <c r="R148" t="n">
+        <v>65</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>1802154878</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1802154878</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>유월네일</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ria0078@naver.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0507-1377-9584</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마장로 137 텐즈힐 근린상가 402동 1층 113호</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yuwol_nail_</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>7</v>
+      </c>
+      <c r="R149" t="n">
+        <v>120</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>1526577269</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1526577269</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>단미네일</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>gleam_yeonjin@naver.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0507-1340-8343</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로13길 1-1 2층 (신금호떡집 2층) or 신금호역 2번출구앞</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sc3fapSc</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>4</v>
+      </c>
+      <c r="R150" t="n">
+        <v>257</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>1922835719</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1922835719</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>아이엠네일</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>gofhd1215@naver.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 274-1</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>2</v>
+      </c>
+      <c r="R151" t="n">
+        <v>15</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>1286301989</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1286301989</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>별별네일</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>gpdnjs1641@naver.com</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로26길 7 2층 별별네일(GS편의점건물)</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/clostar9</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>48</v>
+      </c>
+      <c r="R152" t="n">
+        <v>398</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>1407516344</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1407516344</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>디어마이네일</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>bless_yuna@naver.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0507-1355-7951</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 고산자로8길 31-1 1층</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_rAkXxj</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>4</v>
+      </c>
+      <c r="R153" t="n">
+        <v>134</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>1798673515</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1798673515</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>어썸미뷰티네일</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>awesomeme_@naver.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0507-1337-7517</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로24길 17-1 2층</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/awesomeme_</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>283</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>132</v>
+      </c>
+      <c r="R154" t="n">
+        <v>415</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>1702941561</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1702941561</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>베닛네일</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>purify838@naver.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0507-1343-4794</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 40 상가동 2층 31호</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/purify838</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>9</v>
+      </c>
+      <c r="R155" t="n">
+        <v>52</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2023169077</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2023169077</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>애니네일</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>laboum_day@naver.com</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>070-8874-0706</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로6길 50 성동삼성쉐르빌 123호</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>10</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>35992674</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35992674</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>옥수네일라뜰리에왁싱</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>hee3339@naver.com</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>02-2299-2269</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 223 래미안옥수리버젠 상가 지상 1층 416호</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/l_atelier_beauty</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>236</v>
+      </c>
+      <c r="R157" t="n">
+        <v>241</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>1934541053</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1934541053</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5x5nailstudio</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>fleurievie@naver.com</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0507-1349-1385</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원2길 5 2층</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/5x5nailstudio</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>9</v>
+      </c>
+      <c r="R158" t="n">
+        <v>13</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>1264233280</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1264233280</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>네일 아키비스트</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>jw21st@naver.com</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0507-1381-5204</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 아차산로 107 베컴빌딩 302호</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_hGvAG</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>4</v>
+      </c>
+      <c r="R159" t="n">
+        <v>83</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>1469073588</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1469073588</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>오브림네일</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>kali9578@naver.com</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0507-1335-2849</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 한림말3길 15-12 1층 오브림네일</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_FHeDb</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>17</v>
+      </c>
+      <c r="R160" t="n">
+        <v>134</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>1302158317</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1302158317</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>키키네일 성수</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>m_s_y_0219@naver.com</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0507-1490-5527</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 연무장길 37-7 3층</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kikinail_seongsu</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>2279</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>535</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2814</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>1689817919</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1689817919</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>도토리네일</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>tntpung@naver.com</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0507-1460-2272</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원길 66 1층</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>4</v>
+      </c>
+      <c r="R162" t="n">
+        <v>82</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>1010351084</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1010351084</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>네일반하나</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>hyy204@naver.com</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0507-1337-6251</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 270 대우월드타운상가 2층 211-1호</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_banhana</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>5</v>
+      </c>
+      <c r="R163" t="n">
+        <v>60</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>1829171273</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1829171273</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>마이써니네일</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>tjsduddl_13@naver.com</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로 87 2층 206호</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>http://instagram.com/my_sunny_nail</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>19</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>1332097613</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332097613</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>네일포시즌 성수점</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>nail4season_seongsu@naver.com</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0507-1317-6738</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 아차산로 91 6층</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail4season_seongsu/</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>4852</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>41</v>
+      </c>
+      <c r="R165" t="n">
+        <v>4893</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>1342554268</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1342554268</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>보보네일성수</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>lovewithuu@naver.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>0507-1368-9713</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 아차산로 104 지하1층</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bobonail_kr</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>31</v>
+      </c>
+      <c r="R166" t="n">
+        <v>229</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>1154662700</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1154662700</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>고운손톱</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>won_jieun@naver.com</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>0507-1436-3448</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마장로 137 텐즈힐몰 1층 184호</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/goun__nailshop</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>52</v>
+      </c>
+      <c r="R167" t="n">
+        <v>285</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>1417301812</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1417301812</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>히우네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0507-1369-2519</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수일로3길 4-6 2층</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_Vxafzn</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>3</v>
+      </c>
+      <c r="R168" t="n">
+        <v>23</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>1592997301</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1592997301</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>밴지네일</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sye8894@naver.com</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>0507-1330-5442</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 173 파크자이상가 1층 107호</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_mFiZG</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>12</v>
+      </c>
+      <c r="R169" t="n">
+        <v>199</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>1223711364</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1223711364</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>르베르니 한남점</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>naillove0103@naver.com</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>02-2282-1022</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 168 1층 르베르니 한남점</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_lxokXxj</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>15</v>
+      </c>
+      <c r="R170" t="n">
+        <v>31</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>1299470911</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1299470911</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>태리뷰티</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>in-in-taeri@naver.com</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수일로11길 8 선일빌딩 2층 태리뷰티</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/in_in_taeri</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>333</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>35</v>
+      </c>
+      <c r="R171" t="n">
+        <v>368</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>1635399448</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1635399448</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>단니네일</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>sejin4901871@naver.com</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0507-1342-8319</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 연무장5가길 7 1층 121호</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sejin4901871</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>380</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>60</v>
+      </c>
+      <c r="R172" t="n">
+        <v>440</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>1582611447</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1582611447</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>티스네일</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>tisnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0507-1327-4144</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 140 이편한세상금호파크힐스 상가비동 제지1층 101호</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tisnail</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>26</v>
+      </c>
+      <c r="R173" t="n">
+        <v>54</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>1142233282</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1142233282</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>피아프 네일</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>0226orange@naver.com</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0507-1370-4598</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 광나루로11길 13 1층 102호</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/piaf_nail</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>1</v>
+      </c>
+      <c r="R174" t="n">
+        <v>4</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>1122931590</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1122931590</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>빨강늑대</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>j2hansae@naver.com</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0507-1315-7739</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마조로3길 2 1층 빨강늑대 네일샵</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_redwolf/</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>431</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>91</v>
+      </c>
+      <c r="R175" t="n">
+        <v>522</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>1589180373</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1589180373</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>쿠잉네일</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sungyoojin12@naver.com</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0507-1448-9293</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마장로 137 텐즈힐몰 2층 159호</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/c00ing_nail</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>1</v>
+      </c>
+      <c r="R176" t="n">
+        <v>148</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>1000289725</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1000289725</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>네일바이소아</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>3threesoon@naver.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0507-1370-8054</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 뚝섬로3나길 9 1층</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbysoa/</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>12</v>
+      </c>
+      <c r="R177" t="n">
+        <v>164</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>1144568468</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1144568468</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>시니크랩</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>moyocoyotzin_y@naver.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0507-1345-8557</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원6길 10-1</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sinique_lab</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>11</v>
+      </c>
+      <c r="R178" t="n">
+        <v>40</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>1629415630</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1629415630</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>82네일</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>dbvlftjs82@naver.com</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로6길 50 138호</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://instagram.com/82_nail</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>1</v>
+      </c>
+      <c r="R179" t="n">
+        <v>18</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>1311132484</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1311132484</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>네일슈가</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>kkaeunwoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0507-1407-7529</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 284-1 1층</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>http://instagram.com/1.nail_sugar</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>248</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>38481559</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38481559</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>IT서비스</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>공비서</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>gongbiz@herren.co.kr</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>02-1600-3145</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수일로8길 5</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>http://bit.ly/3LIRnZn</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>1</v>
+      </c>
+      <c r="R181" t="n">
+        <v>1</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>1522367850</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1522367850</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>프랜차이즈본사</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>정원뷰티</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>shawns98@naver.com</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 아차산로 68 에이유빌딩 8층</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://www.allbeauty22.com/</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>31</v>
+      </c>
+      <c r="R182" t="n">
+        <v>31</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
         <is>
           <t>1262366235</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="U182" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1262366235</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
+      <c r="V182" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
